--- a/data/trans_bre/P62-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P62-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,24; -11,9</t>
+          <t>-36,76; -12,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 3,03</t>
+          <t>-19,96; 2,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 2,76</t>
+          <t>-18,2; 2,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 9,99</t>
+          <t>-8,99; 9,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,83; -28,57</t>
+          <t>-65,17; -29,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 7,83</t>
+          <t>-38,69; 7,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 9,13</t>
+          <t>-41,86; 8,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 66,09</t>
+          <t>-32,5; 63,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,37; -25,51</t>
+          <t>-41,65; -26,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,3; -10,01</t>
+          <t>-24,6; -10,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,98; -15,61</t>
+          <t>-29,43; -15,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,79; -4,96</t>
+          <t>-23,77; -4,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -51,47</t>
+          <t>-69,71; -51,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,42; -27,28</t>
+          <t>-55,59; -28,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,57; -37,18</t>
+          <t>-60,83; -37,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,67; -11,69</t>
+          <t>-41,66; -10,56</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-34,68; -14,83</t>
+          <t>-35,19; -14,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,36; -6,54</t>
+          <t>-25,38; -6,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -7,11</t>
+          <t>-24,85; -6,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,26; -9,16</t>
+          <t>-28,5; -8,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,59; -32,11</t>
+          <t>-59,59; -32,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,73; -15,76</t>
+          <t>-50,25; -14,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,93; -16,18</t>
+          <t>-47,49; -15,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,66; -19,03</t>
+          <t>-45,44; -18,28</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,42; -14,68</t>
+          <t>-34,92; -14,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 0,97</t>
+          <t>-17,74; -0,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -2,47</t>
+          <t>-19,78; -3,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,78; -6,33</t>
+          <t>-29,3; -3,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,33; -32,49</t>
+          <t>-60,1; -33,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 2,89</t>
+          <t>-35,52; -0,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,31; -7,54</t>
+          <t>-46,55; -10,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,85; -14,43</t>
+          <t>-45,88; -10,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,81; -16,89</t>
+          <t>-41,16; -17,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 2,14</t>
+          <t>-21,27; 1,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,56; -4,33</t>
+          <t>-28,2; -5,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 3,87</t>
+          <t>-19,65; 4,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,33; -38,33</t>
+          <t>-70,2; -39,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 5,91</t>
+          <t>-47,65; 5,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,79; -9,54</t>
+          <t>-48,97; -11,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 9,76</t>
+          <t>-34,17; 10,36</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,86; -19,98</t>
+          <t>-42,37; -19,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,82; -10,73</t>
+          <t>-31,1; -10,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,01; -13,43</t>
+          <t>-34,35; -14,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,72; -14,22</t>
+          <t>-35,13; -14,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,48; -41,48</t>
+          <t>-68,3; -39,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,75; -25,41</t>
+          <t>-57,87; -26,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,67; -32,11</t>
+          <t>-65,41; -33,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,8; -27,07</t>
+          <t>-52,71; -27,64</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-32,23; -17,95</t>
+          <t>-32,56; -17,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,17; -5,95</t>
+          <t>-19,36; -5,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,74; -5,65</t>
+          <t>-21,56; -5,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 36,16</t>
+          <t>-14,78; 34,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-57,75; -37,63</t>
+          <t>-58,73; -38,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-41,55; -15,36</t>
+          <t>-42,3; -15,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,41; -10,93</t>
+          <t>-38,17; -11,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 79,83</t>
+          <t>-26,59; 72,02</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,01; -30,54</t>
+          <t>-44,42; -30,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,4; -13,06</t>
+          <t>-26,35; -13,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,49; -10,57</t>
+          <t>-22,89; -10,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,51; -20,86</t>
+          <t>-34,59; -21,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,45; -53,03</t>
+          <t>-68,69; -54,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,42; -30,52</t>
+          <t>-51,72; -30,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,57; -23,43</t>
+          <t>-44,29; -23,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,15; -33,15</t>
+          <t>-47,74; -33,21</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -26,51</t>
+          <t>-32,83; -26,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,89; -12,06</t>
+          <t>-18,03; -12,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -13,08</t>
+          <t>-18,94; -13,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 7,24</t>
+          <t>-18,09; 4,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-58,44; -50,7</t>
+          <t>-58,31; -50,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,05; -28,52</t>
+          <t>-39,4; -28,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,92; -29,07</t>
+          <t>-39,55; -29,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 13,63</t>
+          <t>-32,63; 8,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P62-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P62-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>-11,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -12,92</t>
+          <t>-35,97; -11,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 2,95</t>
+          <t>-20,16; 1,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 2,46</t>
+          <t>-18,15; 2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 9,65</t>
+          <t>-11,72; 4,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,17; -29,94</t>
+          <t>-64,83; -27,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 7,79</t>
+          <t>-39,22; 5,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 8,59</t>
+          <t>-43,2; 8,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 63,91</t>
+          <t>-40,84; 28,37</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-14,32</t>
+          <t>-17,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-28,57%</t>
+          <t>-33,72%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,65; -26,08</t>
+          <t>-40,84; -25,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,6; -10,17</t>
+          <t>-24,06; -10,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,43; -15,36</t>
+          <t>-29,66; -15,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,77; -4,76</t>
+          <t>-27,36; -8,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,71; -51,59</t>
+          <t>-68,91; -50,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,59; -28,29</t>
+          <t>-54,98; -27,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,83; -37,19</t>
+          <t>-60,86; -37,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,66; -10,56</t>
+          <t>-45,7; -18,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-18,29</t>
+          <t>-17,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-33,16%</t>
+          <t>-31,88%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-35,19; -14,55</t>
+          <t>-35,1; -15,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,38; -6,08</t>
+          <t>-25,99; -6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -6,45</t>
+          <t>-26,15; -6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,5; -8,71</t>
+          <t>-26,64; -7,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,59; -32,2</t>
+          <t>-59,67; -32,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,25; -14,79</t>
+          <t>-50,39; -16,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,49; -15,05</t>
+          <t>-49,49; -15,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,44; -18,28</t>
+          <t>-44,01; -17,1</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,44</t>
+          <t>-20,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-31,73%</t>
+          <t>-35,78%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,92; -14,62</t>
+          <t>-35,57; -15,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -0,19</t>
+          <t>-17,07; -0,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -3,47</t>
+          <t>-18,82; -2,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,3; -3,99</t>
+          <t>-30,39; -7,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,1; -33,03</t>
+          <t>-60,12; -33,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,52; -0,27</t>
+          <t>-35,34; -0,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -10,02</t>
+          <t>-45,05; -6,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,88; -10,23</t>
+          <t>-48,25; -19,41</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,19</t>
+          <t>-7,55</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-14,78%</t>
+          <t>-15,68%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,16; -17,25</t>
+          <t>-41,98; -18,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 1,86</t>
+          <t>-21,69; 1,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,2; -5,07</t>
+          <t>-27,47; -3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 4,29</t>
+          <t>-21,15; 4,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,2; -39,21</t>
+          <t>-70,5; -39,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 5,73</t>
+          <t>-47,06; 5,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,97; -11,0</t>
+          <t>-48,77; -7,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 10,36</t>
+          <t>-37,03; 10,66</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-24,28</t>
+          <t>-24,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-40,87%</t>
+          <t>-40,85%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -19,2</t>
+          <t>-41,58; -20,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -10,98</t>
+          <t>-30,57; -10,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,35; -14,33</t>
+          <t>-35,12; -15,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,13; -14,71</t>
+          <t>-34,1; -14,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,3; -39,57</t>
+          <t>-68,14; -41,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,87; -26,69</t>
+          <t>-56,57; -24,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,41; -33,52</t>
+          <t>-65,71; -34,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,71; -27,64</t>
+          <t>-52,01; -27,97</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>-14,55</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>-25,29%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-32,56; -17,95</t>
+          <t>-31,51; -17,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,36; -5,87</t>
+          <t>-19,5; -5,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,56; -5,87</t>
+          <t>-21,32; -6,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 34,99</t>
+          <t>-22,58; -6,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,73; -38,17</t>
+          <t>-57,45; -37,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,3; -15,01</t>
+          <t>-41,92; -14,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,17; -11,31</t>
+          <t>-38,02; -12,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 72,02</t>
+          <t>-35,96; -11,76</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-27,92</t>
+          <t>-26,78</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-41,22%</t>
+          <t>-40,64%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,42; -30,88</t>
+          <t>-44,54; -30,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,35; -13,06</t>
+          <t>-26,42; -13,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -10,49</t>
+          <t>-23,21; -10,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,59; -21,01</t>
+          <t>-33,75; -19,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,69; -54,36</t>
+          <t>-68,11; -53,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -30,51</t>
+          <t>-51,47; -29,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,29; -23,34</t>
+          <t>-44,59; -23,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,74; -33,21</t>
+          <t>-48,35; -32,49</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-10,84</t>
+          <t>-18,29</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-20,03%</t>
+          <t>-33,17%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -26,46</t>
+          <t>-32,87; -26,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -12,27</t>
+          <t>-17,89; -11,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,94; -13,36</t>
+          <t>-19,13; -12,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 4,22</t>
+          <t>-21,47; -14,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-58,31; -50,77</t>
+          <t>-58,51; -50,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,4; -28,52</t>
+          <t>-39,21; -27,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -29,79</t>
+          <t>-39,94; -29,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 8,05</t>
+          <t>-37,45; -28,23</t>
         </is>
       </c>
     </row>
